--- a/Checklist_Testes_Urban_Lunch.xlsx
+++ b/Checklist_Testes_Urban_Lunch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Desktop\QA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59AE4840-CFDF-4CFB-B26B-2B18D89A9AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559E3A82-109C-4DEC-A544-2535A64E6F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{98B124E3-5A6E-4A5C-A63A-1111A65B46CC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="89">
   <si>
     <t>Checklist e resultados de teste do aplicativo móvel Urban Lunch</t>
   </si>
@@ -237,12 +237,6 @@
   </si>
   <si>
     <t>Verificar se o texto “Adquira pelo seguinte endereço” é exibido conforme o layout no Figma</t>
-  </si>
-  <si>
-    <t>Verificar se a tela de acompanhamento exibe o tempo restante de preparo, conforme o requisito</t>
-  </si>
-  <si>
-    <t>A tela de acompanhamento não exibe o tempo restante de preparo do prato.</t>
   </si>
   <si>
     <t>Verificar se o valor da entrega é exibido separadamente na tela de confirmação do pedido</t>
@@ -295,12 +289,72 @@
       <t xml:space="preserve"> Pixel 5 (Emulador Android)</t>
     </r>
   </si>
+  <si>
+    <t>Verificar se o rótulo referente ao tempo restante de preparo utiliza “tempo”, conforme o requisito</t>
+  </si>
+  <si>
+    <t>O aplicativo exibe “tiempo” no lugar de “tempo”</t>
+  </si>
+  <si>
+    <t>Link de evidência Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 88 Resultado Real</t>
+  </si>
+  <si>
+    <t>Kan 88 Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 87 Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 87 Resultado Real</t>
+  </si>
+  <si>
+    <t>Kan 89 Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 89 Resultado Real</t>
+  </si>
+  <si>
+    <t>Kan 90 Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 90 Resultado Real</t>
+  </si>
+  <si>
+    <t>Kan 91 Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 91 Resultado Real</t>
+  </si>
+  <si>
+    <t>Kan 92 Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 92 Resultado Real</t>
+  </si>
+  <si>
+    <t>Kan 93 Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 93 Resultado Real</t>
+  </si>
+  <si>
+    <t>Kan 94 Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Kan 94 Resultado Real</t>
+  </si>
+  <si>
+    <t>Kan 86 Resultado Real</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,19 +382,9 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -348,6 +392,27 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -513,17 +578,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -545,28 +599,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -576,32 +628,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -610,39 +658,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -656,13 +686,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -674,8 +704,62 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -988,646 +1072,771 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D869057-033F-42E8-B9CC-0755DB47D700}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="47" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" style="29" customWidth="1"/>
     <col min="2" max="2" width="61.6640625" customWidth="1"/>
     <col min="3" max="3" width="44.21875" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" customWidth="1"/>
-    <col min="5" max="5" width="48.5546875" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="31.5546875" customWidth="1"/>
+    <col min="6" max="6" width="24.77734375" customWidth="1"/>
+    <col min="7" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="30"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="30"/>
+      <c r="B3" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="30"/>
+      <c r="B4" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="24"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+    </row>
+    <row r="9" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="46"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="46"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="1:7" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>3</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="46"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>4</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="46"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>5</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="46"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>6</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="46"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+    </row>
+    <row r="15" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>7</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="46"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="25">
+        <v>8</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="47"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="25">
+        <v>9</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="47"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="25">
+        <v>10</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="47"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="25">
+        <v>11</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="47"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="25">
+        <v>12</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="47"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="25">
+        <v>13</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="47"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="25">
+        <v>14</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="47"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+    </row>
+    <row r="24" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="25">
+        <v>15</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="47"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+    </row>
+    <row r="26" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="26">
+        <v>16</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="50"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+    </row>
+    <row r="27" spans="1:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="25">
+        <v>17</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="51"/>
+      <c r="G27" s="54" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="25">
+        <v>18</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="50"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+    </row>
+    <row r="30" spans="1:7" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="27">
+        <v>19</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="47"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="1:7" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="27">
+        <v>20</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="47"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="1:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="27">
+        <v>21</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="48"/>
-      <c r="B5" s="49" t="s">
+      <c r="C32" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="42"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
-        <v>1</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="13"/>
-    </row>
-    <row r="10" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
-        <v>2</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="13"/>
-    </row>
-    <row r="11" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
-        <v>3</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
-        <v>4</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
-        <v>5</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
-        <v>6</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="D32" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43">
-        <v>8</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="43">
-        <v>9</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="1:5" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="43">
-        <v>10</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="13"/>
-    </row>
-    <row r="20" spans="1:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="43">
-        <v>11</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="43">
-        <v>12</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="1:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="43">
-        <v>13</v>
-      </c>
-      <c r="B22" s="25" t="s">
+      <c r="E32" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="54" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="27">
         <v>22</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="1:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="43">
-        <v>14</v>
-      </c>
-      <c r="B23" s="25" t="s">
+      <c r="B33" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="17"/>
+      <c r="D33" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="47"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="27">
         <v>23</v>
       </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="43">
-        <v>15</v>
-      </c>
-      <c r="B24" s="25" t="s">
+      <c r="B34" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="47"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+    </row>
+    <row r="36" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="27">
         <v>24</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="13"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="B36" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="16"/>
+      <c r="D36" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="17"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
         <v>25</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-    </row>
-    <row r="26" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="44">
-        <v>16</v>
-      </c>
-      <c r="B26" s="25" t="s">
+      <c r="B37" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="17"/>
+      <c r="D37" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="17"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="27">
         <v>26</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="28"/>
-    </row>
-    <row r="27" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="43">
-        <v>17</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="29" t="s">
+      <c r="B38" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="17"/>
+      <c r="D38" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="17"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="39" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="42"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+    </row>
+    <row r="40" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="28">
+        <v>27</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="D40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="48"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+    </row>
+    <row r="41" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="25">
+        <v>28</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="16"/>
+      <c r="D41" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="47"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+    </row>
+    <row r="43" spans="1:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="25">
+        <v>29</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="43">
-        <v>18</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="13"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-    </row>
-    <row r="30" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45">
-        <v>19</v>
-      </c>
-      <c r="B30" s="25" t="s">
+      <c r="E43" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43" s="54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25">
         <v>30</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="13"/>
-    </row>
-    <row r="31" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="45">
-        <v>20</v>
-      </c>
-      <c r="B31" s="26" t="s">
+      <c r="B44" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="G44" s="54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="25">
         <v>31</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="13"/>
-    </row>
-    <row r="32" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="45">
-        <v>21</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="29" t="s">
+      <c r="B45" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E45" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="G45" s="54" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="25">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="45">
-        <v>22</v>
-      </c>
-      <c r="B33" s="26" t="s">
+      <c r="B46" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="G46" s="54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25">
         <v>33</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="13"/>
-    </row>
-    <row r="34" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="45">
-        <v>23</v>
-      </c>
-      <c r="B34" s="25" t="s">
+      <c r="B47" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="F47" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="25">
         <v>34</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="13"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="32" t="s">
+      <c r="B48" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" s="54" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="25">
         <v>35</v>
       </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="33"/>
-    </row>
-    <row r="36" spans="1:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="45">
-        <v>24</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="26"/>
-    </row>
-    <row r="37" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="45">
-        <v>25</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="26"/>
-    </row>
-    <row r="38" spans="1:5" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="45">
-        <v>26</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="26"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-    </row>
-    <row r="40" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="46">
-        <v>27</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="38"/>
-    </row>
-    <row r="41" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="43">
-        <v>28</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="25"/>
-      <c r="D41" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="13"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="8"/>
-    </row>
-    <row r="43" spans="1:5" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="43">
-        <v>29</v>
-      </c>
-      <c r="B43" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="29" t="s">
+      <c r="B49" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="43">
-        <v>30</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D44" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="43">
-        <v>31</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="43">
-        <v>32</v>
-      </c>
-      <c r="B46" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D46" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="43">
-        <v>33</v>
-      </c>
-      <c r="B47" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="43">
-        <v>34</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="43">
-        <v>35</v>
-      </c>
-      <c r="B49" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="30" t="s">
+      <c r="E49" s="53" t="s">
         <v>55</v>
       </c>
+      <c r="F49" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="G49" s="54" t="s">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A42:E42"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="D17:D24 D26:D28 D30:D34 D36:D38 D40:D41 D43:D49 D9:D15" xr:uid="{13973F2E-859E-4758-8F9A-2CB1960E9042}">
@@ -1644,7 +1853,25 @@
     <hyperlink ref="E47" r:id="rId7" xr:uid="{4B6490EE-B856-4669-9BE3-1963B8ACF3DE}"/>
     <hyperlink ref="E48" r:id="rId8" xr:uid="{655D76FC-102F-4D3F-A27E-35AC254D9D97}"/>
     <hyperlink ref="E49" r:id="rId9" xr:uid="{B66336EF-A8B3-45D9-8EBD-B5BACDC3B553}"/>
+    <hyperlink ref="G27" r:id="rId10" xr:uid="{4DADF351-3DD0-404B-838C-740F6BE741AF}"/>
+    <hyperlink ref="G43" r:id="rId11" xr:uid="{B7A7EBB8-75E2-4296-899A-32A1D5195B23}"/>
+    <hyperlink ref="G44" r:id="rId12" xr:uid="{291FF08B-5F8E-4DC1-92F1-EDE0A250918B}"/>
+    <hyperlink ref="G45" r:id="rId13" xr:uid="{2FAE1745-B3ED-43DD-8900-9A26D7A5F26A}"/>
+    <hyperlink ref="G46" r:id="rId14" xr:uid="{927B2A59-4984-4AED-A3DA-929D8711C6E4}"/>
+    <hyperlink ref="G48" r:id="rId15" xr:uid="{FEF47FE5-844D-447F-ABB0-541BB45241BB}"/>
+    <hyperlink ref="G49" r:id="rId16" xr:uid="{D0E1E613-A7EC-42F6-A1F0-FA52CB33B65F}"/>
+    <hyperlink ref="F49" r:id="rId17" xr:uid="{414A92FB-3F83-4B35-BD8A-AABF937E08E4}"/>
+    <hyperlink ref="F48" r:id="rId18" xr:uid="{7BFD2319-DC80-4324-B33A-FD7DA9EB65FF}"/>
+    <hyperlink ref="F46" r:id="rId19" xr:uid="{5629AB78-7DAA-46C9-9FC4-1E81095CB957}"/>
+    <hyperlink ref="F45" r:id="rId20" xr:uid="{B25FEC27-EF4D-4DEE-8493-62C931157210}"/>
+    <hyperlink ref="F44" r:id="rId21" xr:uid="{A3C99DF9-B50C-48B9-B024-7FA2232E1C77}"/>
+    <hyperlink ref="F43" r:id="rId22" xr:uid="{95CFC65D-E582-4F0A-A149-113756F39301}"/>
+    <hyperlink ref="G32" r:id="rId23" xr:uid="{4BED7668-2C8A-447B-BB1C-9BA94F0D13F2}"/>
+    <hyperlink ref="F32" r:id="rId24" xr:uid="{F6CA5C03-D3B3-4911-9A82-03795352B5BA}"/>
+    <hyperlink ref="F47" r:id="rId25" xr:uid="{A6FD785E-C1A8-4D1F-B384-2BC731947DB5}"/>
+    <hyperlink ref="G47" r:id="rId26" xr:uid="{C02B98DC-F9FE-4C47-959E-5C2EBE45F3E5}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
 </worksheet>
 </file>